--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9255506391</v>
+        <v>46157.93111712422</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93111712422</v>
+        <v>46157.93135496967</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93135496967</v>
+        <v>46157.93383432399</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93383432399</v>
+        <v>46157.93695093328</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93695093328</v>
+        <v>46158.2820463444</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2820463444</v>
+        <v>46158.29651782501</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29651782501</v>
+        <v>46158.29806857494</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29806857494</v>
+        <v>46158.33369847106</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33369847106</v>
+        <v>46158.37221331892</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/25. ООО Т2 МОБАЙЛ/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221331892</v>
+        <v>46158.37275223598</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
